--- a/planning/uat/round-0/fixtures-data/two-sheets.xlsx
+++ b/planning/uat/round-0/fixtures-data/two-sheets.xlsx
@@ -60,7 +60,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">UAT IMP-02 184405 item 1</t>
+          <t xml:space="preserve">UAT IMP-02 190749 item 1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -77,7 +77,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">UAT IMP-02 184405 item 2</t>
+          <t xml:space="preserve">UAT IMP-02 190749 item 2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -94,7 +94,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UAT IMP-02 184405 item 3</t>
+          <t xml:space="preserve">UAT IMP-02 190749 item 3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
